--- a/resource/groundTruths/requirement/CF_M04_ground_truth_requirement.xlsx
+++ b/resource/groundTruths/requirement/CF_M04_ground_truth_requirement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/requirement/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74BA8226-AF8A-AE4D-92B8-70537FD76ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDCADEC7-3C89-4149-9EF8-B39A86A1FD5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="900" windowWidth="14480" windowHeight="16680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="160" yWindow="900" windowWidth="14480" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="132">
   <si>
     <t>Document ID</t>
   </si>
@@ -359,64 +359,67 @@
     <t>CF_M04_R38</t>
   </si>
   <si>
-    <t>CF_M06_C06</t>
-  </si>
-  <si>
     <t>Integrity</t>
   </si>
   <si>
-    <t>CF_M06_C07</t>
-  </si>
-  <si>
     <t>Flexibility</t>
   </si>
   <si>
-    <t>CF_M06_C08</t>
-  </si>
-  <si>
     <t>Scalability</t>
   </si>
   <si>
-    <t>CF_M06_C09</t>
-  </si>
-  <si>
     <t>Stability</t>
   </si>
   <si>
-    <t>CF_M06_C10</t>
-  </si>
-  <si>
     <t>Maintenance</t>
   </si>
   <si>
-    <t>CF_M06_C11</t>
-  </si>
-  <si>
     <t>Predictability</t>
   </si>
   <si>
-    <t>CF_M06_C12</t>
-  </si>
-  <si>
     <t>Testability</t>
   </si>
   <si>
-    <t>CF_M06_C13</t>
-  </si>
-  <si>
     <t>Decoupling</t>
   </si>
   <si>
-    <t>CF_M06_C14</t>
-  </si>
-  <si>
     <t>Modularity</t>
   </si>
   <si>
-    <t>CF_M06_C15</t>
-  </si>
-  <si>
     <t>Sustainability</t>
+  </si>
+  <si>
+    <t>*CF_M06_C06</t>
+  </si>
+  <si>
+    <t>*CF_M06_C07</t>
+  </si>
+  <si>
+    <t>*CF_M06_C08</t>
+  </si>
+  <si>
+    <t>*CF_M06_C09</t>
+  </si>
+  <si>
+    <t>*CF_M06_C10</t>
+  </si>
+  <si>
+    <t>*CF_M06_C11</t>
+  </si>
+  <si>
+    <t>*CF_M06_C12</t>
+  </si>
+  <si>
+    <t>*CF_M06_C13</t>
+  </si>
+  <si>
+    <t>*CF_M06_C14</t>
+  </si>
+  <si>
+    <t>*CF_M06_C15</t>
+  </si>
+  <si>
+    <t>Concept</t>
   </si>
 </sst>
 </file>
@@ -811,7 +814,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>131</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
@@ -1792,82 +1795,82 @@
     </row>
     <row r="12" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="B12" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="B13" s="4" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="B14" s="4" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="B15" s="4" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="B16" s="4" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="16" x14ac:dyDescent="0.2">
       <c r="B17" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="16" x14ac:dyDescent="0.2">
       <c r="B18" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="16" x14ac:dyDescent="0.2">
       <c r="B19" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="16" x14ac:dyDescent="0.2">
       <c r="B20" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="16" x14ac:dyDescent="0.2">
       <c r="B21" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/resource/groundTruths/requirement/CF_M04_ground_truth_requirement.xlsx
+++ b/resource/groundTruths/requirement/CF_M04_ground_truth_requirement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/requirement/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B87A6DE1-704D-A24C-AD33-D8128055B63A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F3F7339-5D66-704F-A5C8-A444FCDF1C38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="160" yWindow="900" windowWidth="14480" windowHeight="16680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -380,40 +380,40 @@
     <t>Sustainability</t>
   </si>
   <si>
-    <t>*CF_M06_C06</t>
-  </si>
-  <si>
-    <t>*CF_M06_C07</t>
-  </si>
-  <si>
-    <t>*CF_M06_C08</t>
-  </si>
-  <si>
-    <t>*CF_M06_C09</t>
-  </si>
-  <si>
-    <t>*CF_M06_C10</t>
-  </si>
-  <si>
-    <t>*CF_M06_C11</t>
-  </si>
-  <si>
-    <t>*CF_M06_C12</t>
-  </si>
-  <si>
-    <t>*CF_M06_C13</t>
-  </si>
-  <si>
-    <t>*CF_M06_C14</t>
-  </si>
-  <si>
-    <t>*CF_M06_C15</t>
-  </si>
-  <si>
     <t>Concept</t>
   </si>
   <si>
     <t>Fixed Type</t>
+  </si>
+  <si>
+    <t>*CF_M04_C06</t>
+  </si>
+  <si>
+    <t>*CF_M04_C07</t>
+  </si>
+  <si>
+    <t>*CF_M04_C08</t>
+  </si>
+  <si>
+    <t>*CF_M04_C09</t>
+  </si>
+  <si>
+    <t>*CF_M04_C10</t>
+  </si>
+  <si>
+    <t>*CF_M04_C11</t>
+  </si>
+  <si>
+    <t>*CF_M04_C12</t>
+  </si>
+  <si>
+    <t>*CF_M04_C13</t>
+  </si>
+  <si>
+    <t>*CF_M04_C14</t>
+  </si>
+  <si>
+    <t>*CF_M04_C15</t>
   </si>
 </sst>
 </file>
@@ -806,7 +806,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
@@ -815,7 +815,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" x14ac:dyDescent="0.2">
@@ -1727,7 +1727,7 @@
     </row>
     <row r="12" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="B12" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>108</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="13" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="B13" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>109</v>
@@ -1743,7 +1743,7 @@
     </row>
     <row r="14" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="B14" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>110</v>
@@ -1751,7 +1751,7 @@
     </row>
     <row r="15" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="B15" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>111</v>
@@ -1759,7 +1759,7 @@
     </row>
     <row r="16" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="B16" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>112</v>
@@ -1767,7 +1767,7 @@
     </row>
     <row r="17" spans="2:3" ht="16" x14ac:dyDescent="0.2">
       <c r="B17" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>113</v>
@@ -1775,7 +1775,7 @@
     </row>
     <row r="18" spans="2:3" ht="16" x14ac:dyDescent="0.2">
       <c r="B18" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>114</v>
@@ -1783,7 +1783,7 @@
     </row>
     <row r="19" spans="2:3" ht="16" x14ac:dyDescent="0.2">
       <c r="B19" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>115</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="20" spans="2:3" ht="16" x14ac:dyDescent="0.2">
       <c r="B20" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>116</v>
@@ -1799,7 +1799,7 @@
     </row>
     <row r="21" spans="2:3" ht="16" x14ac:dyDescent="0.2">
       <c r="B21" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>117</v>
